--- a/experiment_log.xlsx
+++ b/experiment_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,25 @@
         <v>0</v>
       </c>
       <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-23T16:19:13.273578</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>test_epics_arm_20260923_161913.h5</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/experiment_log.xlsx
+++ b/experiment_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +499,29 @@
         <v>0</v>
       </c>
       <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-24T13:10:26.629090</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>remote_test_6626_20260924_131026.h5</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Remote PC DAQ test</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/experiment_log.xlsx
+++ b/experiment_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,6 +523,170 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:51:18.895369</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>exp_run_20260924_165118.h5</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:51:21.704335</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>exp_run_20260924_165121.h5</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:51:29.133207</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>exp_run_20260924_165129.h5</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:51:49.840853</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>exp_run_20260924_165149.h5</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:51:56.253069</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>exp_run_20260924_165156.h5</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-26T20:35:19.049504</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>remote_test_6117_20260926_203518.h5</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Remote PC DAQ test</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-26T20:37:39.997652</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>remote_test_6117_20260926_203739.h5</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Remote PC DAQ test</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-26T20:37:51.594769</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>remote_test_6117_20260926_203751.h5</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Remote PC DAQ test</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/experiment_log.xlsx
+++ b/experiment_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,6 +687,25 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-26T22:14:37.240508</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>exp_run_20260926_221437.h5</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
